--- a/data-source/COMPRAQUIMICOSPARAGUAI.xlsx
+++ b/data-source/COMPRAQUIMICOSPARAGUAI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E32ED126-E204-4A58-A04C-48A039261271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{E32ED126-E204-4A58-A04C-48A039261271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB83B8A0-4BE1-4626-9CB3-D0D8D696F7AC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3DC5B5D5-6241-4173-978A-8273E3297297}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="20">
   <si>
     <t>Núm.OC</t>
   </si>
@@ -75,6 +75,30 @@
   </si>
   <si>
     <t>PIGMENTO IMPORTADO</t>
+  </si>
+  <si>
+    <t>RESINA LX-50B (AMERICA ASIA)</t>
+  </si>
+  <si>
+    <t>RESINA IMPORTADA</t>
+  </si>
+  <si>
+    <t>RESINA LX-30B (AMERICA ASIA)</t>
+  </si>
+  <si>
+    <t>RESINA FU6080 (AMERICA ASIA)</t>
+  </si>
+  <si>
+    <t>F9209A - Pu Resin</t>
+  </si>
+  <si>
+    <t>JF-HSY-BY100 - Pu Resin</t>
+  </si>
+  <si>
+    <t>JF-HSY-BY002 - Pu Resin</t>
+  </si>
+  <si>
+    <t>F9207A-1 - Pu Resin</t>
   </si>
 </sst>
 </file>
@@ -480,7 +504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C47A0A13-0C66-4D0D-9211-384DF89879FB}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
@@ -657,6 +681,259 @@
         <v>2.23</v>
       </c>
     </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>34</v>
+      </c>
+      <c r="B8" s="2">
+        <v>11370</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>9180</v>
+      </c>
+      <c r="G8" s="4">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>34</v>
+      </c>
+      <c r="B9" s="2">
+        <v>16336</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9">
+        <v>9360</v>
+      </c>
+      <c r="G9" s="4">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>34</v>
+      </c>
+      <c r="B10" s="2">
+        <v>16684</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10">
+        <v>2880</v>
+      </c>
+      <c r="G10" s="4">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>34</v>
+      </c>
+      <c r="B11" s="2">
+        <v>4478</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11">
+        <v>9</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11">
+        <v>500</v>
+      </c>
+      <c r="G11" s="4">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>34</v>
+      </c>
+      <c r="B12" s="2">
+        <v>5797</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>9</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12">
+        <v>1000</v>
+      </c>
+      <c r="G12" s="4">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>34</v>
+      </c>
+      <c r="B13" s="2">
+        <v>6506</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13">
+        <v>9</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13">
+        <v>1000</v>
+      </c>
+      <c r="G13" s="4">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14">
+        <v>9</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14">
+        <v>190</v>
+      </c>
+      <c r="G14" s="4">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>34</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15">
+        <v>9</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15" s="4">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>34</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16">
+        <v>9</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="G16" s="4">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>34</v>
+      </c>
+      <c r="B17" s="2">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17">
+        <v>9</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17">
+        <v>5</v>
+      </c>
+      <c r="G17" s="4">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>34</v>
+      </c>
+      <c r="B18" s="2">
+        <v>5</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18">
+        <v>9</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18">
+        <v>190</v>
+      </c>
+      <c r="G18" s="4">
+        <v>2.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data-source/COMPRAQUIMICOSPARAGUAI.xlsx
+++ b/data-source/COMPRAQUIMICOSPARAGUAI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="43" documentId="8_{E32ED126-E204-4A58-A04C-48A039261271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB83B8A0-4BE1-4626-9CB3-D0D8D696F7AC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3DC5B5D5-6241-4173-978A-8273E3297297}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="20736" windowHeight="11148" xr2:uid="{3DC5B5D5-6241-4173-978A-8273E3297297}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>

--- a/data-source/COMPRAQUIMICOSPARAGUAI.xlsx
+++ b/data-source/COMPRAQUIMICOSPARAGUAI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{E32ED126-E204-4A58-A04C-48A039261271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB83B8A0-4BE1-4626-9CB3-D0D8D696F7AC}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{E32ED126-E204-4A58-A04C-48A039261271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{916B09C8-E99C-4A23-B1A9-7CF33A919112}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="20736" windowHeight="11148" xr2:uid="{3DC5B5D5-6241-4173-978A-8273E3297297}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3DC5B5D5-6241-4173-978A-8273E3297297}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -124,7 +124,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -134,6 +134,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -164,12 +170,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -544,395 +551,412 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>13</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="A2" s="2">
+        <v>13</v>
+      </c>
+      <c r="B2" s="3">
         <v>4478</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" s="2">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>1000</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="5">
         <v>2.14</v>
       </c>
+      <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="A3" s="2">
+        <v>13</v>
+      </c>
+      <c r="B3" s="3">
         <v>5797</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>1000</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="5">
         <v>1.86</v>
       </c>
+      <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="A4" s="2">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3">
         <v>6506</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" s="2">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>1000</v>
       </c>
-      <c r="G4" s="4">
-        <v>2.23</v>
-      </c>
+      <c r="G4" s="5">
+        <v>2.23</v>
+      </c>
+      <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="A5" s="2">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3">
         <v>4478</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D5">
-        <v>9</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D5" s="2">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>500</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="5">
         <v>2.14</v>
       </c>
+      <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="A6" s="2">
+        <v>13</v>
+      </c>
+      <c r="B6" s="3">
         <v>5797</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="C6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2">
+        <v>9</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>500</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="5">
         <v>1.86</v>
       </c>
+      <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="A7" s="2">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3">
         <v>6506</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D7">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" s="2">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>500</v>
       </c>
-      <c r="G7" s="4">
-        <v>2.23</v>
-      </c>
+      <c r="G7" s="5">
+        <v>2.23</v>
+      </c>
+      <c r="H7" s="2"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>34</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="A8" s="2">
+        <v>34</v>
+      </c>
+      <c r="B8" s="3">
         <v>11370</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D8">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8">
+      <c r="D8" s="2">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="2">
         <v>9180</v>
       </c>
-      <c r="G8" s="4">
-        <v>2.23</v>
-      </c>
+      <c r="G8" s="5">
+        <v>2.23</v>
+      </c>
+      <c r="H8" s="2"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>34</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="A9" s="2">
+        <v>34</v>
+      </c>
+      <c r="B9" s="3">
         <v>16336</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D9">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9">
+      <c r="D9" s="2">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="2">
         <v>9360</v>
       </c>
-      <c r="G9" s="4">
-        <v>2.23</v>
-      </c>
+      <c r="G9" s="5">
+        <v>2.23</v>
+      </c>
+      <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>34</v>
-      </c>
-      <c r="B10" s="2">
+      <c r="A10" s="2">
+        <v>34</v>
+      </c>
+      <c r="B10" s="3">
         <v>16684</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D10">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10">
+      <c r="D10" s="2">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="2">
         <v>2880</v>
       </c>
-      <c r="G10" s="4">
-        <v>2.23</v>
-      </c>
+      <c r="G10" s="5">
+        <v>2.23</v>
+      </c>
+      <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>34</v>
-      </c>
-      <c r="B11" s="2">
+      <c r="A11" s="2">
+        <v>34</v>
+      </c>
+      <c r="B11" s="3">
         <v>4478</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D11">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="D11" s="2">
+        <v>9</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>500</v>
       </c>
-      <c r="G11" s="4">
-        <v>2.23</v>
-      </c>
+      <c r="G11" s="5">
+        <v>2.23</v>
+      </c>
+      <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>34</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="A12" s="2">
+        <v>34</v>
+      </c>
+      <c r="B12" s="3">
         <v>5797</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="C12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2">
+        <v>9</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>1000</v>
       </c>
-      <c r="G12" s="4">
-        <v>2.23</v>
-      </c>
+      <c r="G12" s="5">
+        <v>2.23</v>
+      </c>
+      <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>34</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="A13" s="2">
+        <v>34</v>
+      </c>
+      <c r="B13" s="3">
         <v>6506</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D13">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="D13" s="2">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>1000</v>
       </c>
-      <c r="G13" s="4">
-        <v>2.23</v>
-      </c>
+      <c r="G13" s="5">
+        <v>2.23</v>
+      </c>
+      <c r="H13" s="2"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>34</v>
-      </c>
-      <c r="B14" s="2">
+      <c r="A14" s="2">
+        <v>34</v>
+      </c>
+      <c r="B14" s="3">
         <v>1</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D14">
-        <v>9</v>
-      </c>
-      <c r="E14" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14">
+      <c r="D14" s="2">
+        <v>9</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2">
         <v>190</v>
       </c>
-      <c r="G14" s="4">
-        <v>2.23</v>
-      </c>
+      <c r="G14" s="5">
+        <v>2.23</v>
+      </c>
+      <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>34</v>
-      </c>
-      <c r="B15" s="2">
+      <c r="A15" s="2">
+        <v>34</v>
+      </c>
+      <c r="B15" s="3">
         <v>2</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D15">
-        <v>9</v>
-      </c>
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15">
+      <c r="D15" s="2">
+        <v>9</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="2">
         <v>5</v>
       </c>
-      <c r="G15" s="4">
-        <v>2.23</v>
-      </c>
+      <c r="G15" s="5">
+        <v>2.23</v>
+      </c>
+      <c r="H15" s="2"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>34</v>
-      </c>
-      <c r="B16" s="2">
+      <c r="A16" s="2">
+        <v>34</v>
+      </c>
+      <c r="B16" s="3">
         <v>3</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D16">
-        <v>9</v>
-      </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16">
+      <c r="D16" s="2">
+        <v>9</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="2">
         <v>5</v>
       </c>
-      <c r="G16" s="4">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>34</v>
-      </c>
-      <c r="B17" s="2">
+      <c r="G16" s="5">
+        <v>2.23</v>
+      </c>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>34</v>
+      </c>
+      <c r="B17" s="3">
         <v>4</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D17">
-        <v>9</v>
-      </c>
-      <c r="E17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17">
+      <c r="D17" s="2">
+        <v>9</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="2">
         <v>5</v>
       </c>
-      <c r="G17" s="4">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>34</v>
-      </c>
-      <c r="B18" s="2">
+      <c r="G17" s="5">
+        <v>2.23</v>
+      </c>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>34</v>
+      </c>
+      <c r="B18" s="3">
         <v>5</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D18">
-        <v>9</v>
-      </c>
-      <c r="E18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18">
+      <c r="D18" s="2">
+        <v>9</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="2">
         <v>190</v>
       </c>
-      <c r="G18" s="4">
-        <v>2.23</v>
-      </c>
+      <c r="G18" s="5">
+        <v>2.23</v>
+      </c>
+      <c r="H18" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/data-source/COMPRAQUIMICOSPARAGUAI.xlsx
+++ b/data-source/COMPRAQUIMICOSPARAGUAI.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/QUIMICOS-ANALISE/data-source/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\impre\Downloads\QUIMICOS-ANALISE-QUIMICOS-V3\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="48" documentId="8_{E32ED126-E204-4A58-A04C-48A039261271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{916B09C8-E99C-4A23-B1A9-7CF33A919112}"/>
@@ -122,6 +122,7 @@
       <sz val="11"/>
       <color rgb="FF800000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
